--- a/StructureDefinition-corneal-tomography-report.xlsx
+++ b/StructureDefinition-corneal-tomography-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T00:41:24+00:00</t>
+    <t>2026-08-25T02:25:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-corneal-tomography-report.xlsx
+++ b/StructureDefinition-corneal-tomography-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T02:25:39+00:00</t>
+    <t>2026-08-25T18:52:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-corneal-tomography-report.xlsx
+++ b/StructureDefinition-corneal-tomography-report.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>0.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T18:52:20+00:00</t>
+    <t>2026-09-01T17:43:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -658,7 +658,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/CodeSystem/v2-0074</t>
+    <t>http://terminology.hl7.org/ValueSet/v2-0074</t>
   </si>
   <si>
     <t>DiagnosticReport.code</t>
@@ -909,7 +909,7 @@
 Atomic ValueResultAtomic resultDataTestAnalyteBatteryOrganizer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Observation|4.0.1)
+    <t xml:space="preserve">Reference(https://YasniiSS.github.io/fhir4eyes/StructureDefinition/ct-anterior-surface|https://YasniiSS.github.io/fhir4eyes/StructureDefinition/ct-posterior-surface|https://YasniiSS.github.io/fhir4eyes/StructureDefinition/ct-pachymetry|https://YasniiSS.github.io/fhir4eyes/StructureDefinition/ct-anterior-chamber|https://YasniiSS.github.io/fhir4eyes/StructureDefinition/ct-keratoconus-indices|https://YasniiSS.github.io/fhir4eyes/StructureDefinition/ct-densitometry)
 </t>
   </si>
   <si>
@@ -1449,7 +1449,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="75.25390625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
